--- a/branches/dev/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
+++ b/branches/dev/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T10:39:42+00:00</t>
+    <t>2026-07-23T11:20:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
+++ b/branches/dev/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T11:20:28+00:00</t>
+    <t>2026-07-23T15:55:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
+++ b/branches/dev/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T15:55:45+00:00</t>
+    <t>2026-07-24T06:29:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
+++ b/branches/dev/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T10:43:48+00:00</t>
+    <t>2026-09-03T17:01:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
+++ b/branches/dev/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T17:01:55+00:00</t>
+    <t>2026-09-04T05:29:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
+++ b/branches/dev/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T05:29:06+00:00</t>
+    <t>2026-09-04T06:37:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
+++ b/branches/dev/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T06:37:14+00:00</t>
+    <t>2026-09-04T07:02:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
+++ b/branches/dev/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T07:02:52+00:00</t>
+    <t>2026-09-04T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
+++ b/branches/dev/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T08:01:15+00:00</t>
+    <t>2026-09-04T11:35:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
+++ b/branches/dev/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T11:35:42+00:00</t>
+    <t>2026-09-04T11:52:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
+++ b/branches/dev/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T11:52:20+00:00</t>
+    <t>2026-09-04T12:44:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
+++ b/branches/dev/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T12:44:12+00:00</t>
+    <t>2026-09-04T13:01:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
+++ b/branches/dev/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T13:01:37+00:00</t>
+    <t>2026-09-04T16:11:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
+++ b/branches/dev/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T16:11:50+00:00</t>
+    <t>2026-09-04T16:57:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
+++ b/branches/dev/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T16:57:12+00:00</t>
+    <t>2026-09-07T15:50:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
+++ b/branches/dev/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T15:50:41+00:00</t>
+    <t>2026-09-07T16:06:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
+++ b/branches/dev/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T16:06:13+00:00</t>
+    <t>2026-09-08T09:14:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
+++ b/branches/dev/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T09:14:37+00:00</t>
+    <t>2026-09-08T09:32:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
+++ b/branches/dev/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T09:32:56+00:00</t>
+    <t>2026-09-08T15:03:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
+++ b/branches/dev/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T15:03:47+00:00</t>
+    <t>2026-09-09T09:29:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
+++ b/branches/dev/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T09:29:55+00:00</t>
+    <t>2026-09-09T10:02:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
+++ b/branches/dev/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T10:02:49+00:00</t>
+    <t>2026-09-09T11:08:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
+++ b/branches/dev/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T11:08:17+00:00</t>
+    <t>2026-09-09T11:49:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
+++ b/branches/dev/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10070" uniqueCount="916">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10070" uniqueCount="917">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T11:49:20+00:00</t>
+    <t>2026-09-11T10:52:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -278,7 +278,7 @@
   </si>
   <si>
     <t>con-3:Condition.clinicalStatus SHALL be present if verificationStatus is not entered-in-error and category is problem-list-item {clinicalStatus.exists() or verificationStatus.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-ver-status' and code = 'entered-in-error').exists() or category.select($this='problem-list-item').empty()}
-con-4:If condition is abated, then clinicalStatus must be either inactive, resolved, or remission {abatement.empty() or clinicalStatus.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-clinical' and (code='resolved' or code='remission' or code='inactive')).exists()}con-5:Condition.clinicalStatus SHALL NOT be present if verification Status is entered-in-error {verificationStatus.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-ver-status' and code='entered-in-error').empty() or clinicalStatus.empty()}dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}se-genetic-evidence:Genetic diagnosis must have at least one evidence.detail referencing a MolGen resource {evidence.exists() and evidence.detail.exists()}</t>
+con-4:If condition is abated, then clinicalStatus must be either inactive, resolved, or remission {abatement.empty() or clinicalStatus.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-clinical' and (code='resolved' or code='remission' or code='inactive')).exists()}con-5:Condition.clinicalStatus SHALL NOT be present if verification Status is entered-in-error {verificationStatus.coding.where(system='http://terminology.hl7.org/CodeSystem/condition-ver-status' and code='entered-in-error').empty() or clinicalStatus.empty()}dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>anamneseUndDiagnostik.genetischeDiagnose</t>
@@ -1061,7 +1061,7 @@
     <t>Kategorisierung als genetische Erkrankung</t>
   </si>
   <si>
-    <t>Pflicht-Kategorie zur Kennzeichnung als genetisch bestätigte Erkrankung</t>
+    <t>Pflicht-Kategorie zur Kennzeichnung als genetisch bestätigte Erkrankung. Bewusste Nutzung der extensible-Bindung von Condition.category: Der Wert bezeichnet nicht die Rolle im Datensatz, sondern macht die genetische Sicherung registeruebergreifend auswertbar.</t>
   </si>
   <si>
     <t>The categorization is often highly contextual and may appear poorly differentiated or not very useful in other contexts.</t>
@@ -1641,6 +1641,9 @@
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
   &lt;system value="http://omim.org"/&gt;
 &lt;/valueCoding&gt;</t>
+  </si>
+  <si>
+    <t>anamneseUndDiagnostik.genetischeDiagnose.omimCode</t>
   </si>
   <si>
     <t>Condition.code.coding:omim.id</t>
@@ -19100,7 +19103,7 @@
         <v>104</v>
       </c>
       <c r="AK129" t="s" s="2">
-        <v>87</v>
+        <v>519</v>
       </c>
       <c r="AL129" t="s" s="2">
         <v>369</v>
@@ -19123,7 +19126,7 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B130" t="s" s="2">
         <v>379</v>
@@ -19244,7 +19247,7 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B131" t="s" s="2">
         <v>381</v>
@@ -19367,7 +19370,7 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B132" t="s" s="2">
         <v>446</v>
@@ -19492,7 +19495,7 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B133" t="s" s="2">
         <v>450</v>
@@ -19615,7 +19618,7 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B134" t="s" s="2">
         <v>454</v>
@@ -19738,7 +19741,7 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B135" t="s" s="2">
         <v>460</v>
@@ -19861,7 +19864,7 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B136" t="s" s="2">
         <v>462</v>
@@ -19986,10 +19989,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -20091,7 +20094,7 @@
         <v>80</v>
       </c>
       <c r="AL137" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AM137" t="s" s="2">
         <v>80</v>
@@ -20111,10 +20114,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -20140,13 +20143,13 @@
         <v>250</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
@@ -20175,10 +20178,10 @@
         <v>157</v>
       </c>
       <c r="Y138" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="Z138" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AA138" t="s" s="2">
         <v>80</v>
@@ -20196,7 +20199,7 @@
         <v>80</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>81</v>
@@ -20214,13 +20217,13 @@
         <v>80</v>
       </c>
       <c r="AL138" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AM138" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN138" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AO138" t="s" s="2">
         <v>80</v>
@@ -20229,15 +20232,15 @@
         <v>80</v>
       </c>
       <c r="AQ138" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -20355,10 +20358,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -20478,13 +20481,13 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="B141" t="s" s="2">
         <v>539</v>
       </c>
-      <c r="B141" t="s" s="2">
-        <v>538</v>
-      </c>
       <c r="C141" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D141" t="s" s="2">
         <v>80</v>
@@ -20506,13 +20509,13 @@
         <v>80</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" s="2"/>
@@ -20601,10 +20604,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -20676,7 +20679,7 @@
         <v>80</v>
       </c>
       <c r="AB142" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AC142" s="2"/>
       <c r="AD142" t="s" s="2">
@@ -20724,13 +20727,13 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C143" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D143" t="s" s="2">
         <v>80</v>
@@ -20793,7 +20796,7 @@
       </c>
       <c r="Y143" s="2"/>
       <c r="Z143" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AA143" t="s" s="2">
         <v>80</v>
@@ -20849,10 +20852,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -20970,10 +20973,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -21093,10 +21096,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -21141,7 +21144,7 @@
         <v>80</v>
       </c>
       <c r="S146" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="T146" t="s" s="2">
         <v>80</v>
@@ -21218,10 +21221,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -21341,10 +21344,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -21464,10 +21467,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -21587,10 +21590,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -21712,10 +21715,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -21837,14 +21840,14 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="E152" s="2"/>
       <c r="F152" t="s" s="2">
@@ -21863,17 +21866,17 @@
         <v>93</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="P152" t="s" s="2">
         <v>80</v>
@@ -21922,7 +21925,7 @@
         <v>80</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>92</v>
@@ -21937,22 +21940,22 @@
         <v>104</v>
       </c>
       <c r="AK152" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AL152" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM152" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AN152" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO152" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AP152" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AQ152" t="s" s="2">
         <v>80</v>
@@ -21960,10 +21963,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -22081,10 +22084,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -22204,10 +22207,10 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -22233,13 +22236,13 @@
         <v>106</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="O155" s="2"/>
       <c r="P155" t="s" s="2">
@@ -22289,7 +22292,7 @@
         <v>80</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>81</v>
@@ -22298,7 +22301,7 @@
         <v>92</v>
       </c>
       <c r="AI155" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AJ155" t="s" s="2">
         <v>104</v>
@@ -22327,10 +22330,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -22356,13 +22359,13 @@
         <v>133</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="O156" s="2"/>
       <c r="P156" t="s" s="2">
@@ -22391,10 +22394,10 @@
         <v>149</v>
       </c>
       <c r="Y156" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="Z156" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AA156" t="s" s="2">
         <v>80</v>
@@ -22412,7 +22415,7 @@
         <v>80</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>81</v>
@@ -22450,10 +22453,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -22479,13 +22482,13 @@
         <v>242</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="O157" s="2"/>
       <c r="P157" t="s" s="2">
@@ -22535,7 +22538,7 @@
         <v>80</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>81</v>
@@ -22573,10 +22576,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -22602,13 +22605,13 @@
         <v>106</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="O158" s="2"/>
       <c r="P158" t="s" s="2">
@@ -22658,7 +22661,7 @@
         <v>80</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>81</v>
@@ -22696,10 +22699,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -22722,16 +22725,16 @@
         <v>93</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="O159" s="2"/>
       <c r="P159" t="s" s="2">
@@ -22781,7 +22784,7 @@
         <v>80</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>81</v>
@@ -22796,22 +22799,22 @@
         <v>104</v>
       </c>
       <c r="AK159" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AL159" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM159" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AN159" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO159" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AP159" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AQ159" t="s" s="2">
         <v>80</v>
@@ -22819,10 +22822,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -22940,10 +22943,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -23063,10 +23066,10 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -23092,13 +23095,13 @@
         <v>106</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="N162" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="O162" s="2"/>
       <c r="P162" t="s" s="2">
@@ -23148,7 +23151,7 @@
         <v>80</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>81</v>
@@ -23157,7 +23160,7 @@
         <v>92</v>
       </c>
       <c r="AI162" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AJ162" t="s" s="2">
         <v>104</v>
@@ -23186,10 +23189,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -23215,13 +23218,13 @@
         <v>133</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="O163" s="2"/>
       <c r="P163" t="s" s="2">
@@ -23250,10 +23253,10 @@
         <v>149</v>
       </c>
       <c r="Y163" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="Z163" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AA163" t="s" s="2">
         <v>80</v>
@@ -23271,7 +23274,7 @@
         <v>80</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>81</v>
@@ -23309,10 +23312,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -23338,13 +23341,13 @@
         <v>242</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="O164" s="2"/>
       <c r="P164" t="s" s="2">
@@ -23394,7 +23397,7 @@
         <v>80</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>81</v>
@@ -23432,10 +23435,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -23461,13 +23464,13 @@
         <v>106</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="O165" s="2"/>
       <c r="P165" t="s" s="2">
@@ -23517,7 +23520,7 @@
         <v>80</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>81</v>
@@ -23555,10 +23558,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -23581,16 +23584,16 @@
         <v>93</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="O166" s="2"/>
       <c r="P166" t="s" s="2">
@@ -23628,17 +23631,17 @@
         <v>80</v>
       </c>
       <c r="AB166" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AC166" s="2"/>
       <c r="AD166" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE166" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>81</v>
@@ -23653,22 +23656,22 @@
         <v>104</v>
       </c>
       <c r="AK166" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AL166" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AM166" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AN166" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO166" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AP166" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AQ166" t="s" s="2">
         <v>80</v>
@@ -23676,13 +23679,13 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C167" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="D167" t="s" s="2">
         <v>80</v>
@@ -23707,13 +23710,13 @@
         <v>228</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="O167" s="2"/>
       <c r="P167" t="s" s="2">
@@ -23763,7 +23766,7 @@
         <v>80</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>81</v>
@@ -23784,16 +23787,16 @@
         <v>80</v>
       </c>
       <c r="AM167" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AN167" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO167" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AP167" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AQ167" t="s" s="2">
         <v>80</v>
@@ -23801,13 +23804,13 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C168" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="D168" t="s" s="2">
         <v>80</v>
@@ -23829,16 +23832,16 @@
         <v>93</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="N168" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="O168" s="2"/>
       <c r="P168" t="s" s="2">
@@ -23888,7 +23891,7 @@
         <v>80</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>81</v>
@@ -23906,19 +23909,19 @@
         <v>80</v>
       </c>
       <c r="AL168" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="AM168" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AN168" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO168" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AP168" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AQ168" t="s" s="2">
         <v>80</v>
@@ -23926,10 +23929,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -24047,10 +24050,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -24170,10 +24173,10 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -24199,13 +24202,13 @@
         <v>228</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="N171" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="O171" s="2"/>
       <c r="P171" t="s" s="2">
@@ -24255,7 +24258,7 @@
         <v>80</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>81</v>
@@ -24264,7 +24267,7 @@
         <v>92</v>
       </c>
       <c r="AI171" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="AJ171" t="s" s="2">
         <v>104</v>
@@ -24273,7 +24276,7 @@
         <v>80</v>
       </c>
       <c r="AL171" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="AM171" t="s" s="2">
         <v>80</v>
@@ -24282,7 +24285,7 @@
         <v>80</v>
       </c>
       <c r="AO171" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="AP171" t="s" s="2">
         <v>80</v>
@@ -24293,10 +24296,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -24322,10 +24325,10 @@
         <v>106</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="N172" s="2"/>
       <c r="O172" s="2"/>
@@ -24414,10 +24417,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -24533,13 +24536,13 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="B174" t="s" s="2">
         <v>656</v>
       </c>
-      <c r="B174" t="s" s="2">
-        <v>655</v>
-      </c>
       <c r="C174" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="D174" t="s" s="2">
         <v>80</v>
@@ -24561,7 +24564,7 @@
         <v>80</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="L174" t="s" s="2">
         <v>385</v>
@@ -24656,10 +24659,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -24777,10 +24780,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -24900,10 +24903,10 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -24943,7 +24946,7 @@
       </c>
       <c r="Q177" s="2"/>
       <c r="R177" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="S177" t="s" s="2">
         <v>80</v>
@@ -25023,10 +25026,10 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -25124,7 +25127,7 @@
         <v>80</v>
       </c>
       <c r="AL178" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="AM178" t="s" s="2">
         <v>80</v>
@@ -25144,10 +25147,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -25265,10 +25268,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -25388,10 +25391,10 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -25454,10 +25457,10 @@
         <v>254</v>
       </c>
       <c r="Y181" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="Z181" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="AA181" t="s" s="2">
         <v>80</v>
@@ -25513,10 +25516,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -25634,10 +25637,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -25757,10 +25760,10 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -25882,10 +25885,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -26005,10 +26008,10 @@
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -26130,10 +26133,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -26255,10 +26258,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -26380,10 +26383,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -26505,10 +26508,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -26534,10 +26537,10 @@
         <v>228</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="N190" s="2"/>
       <c r="O190" s="2"/>
@@ -26588,7 +26591,7 @@
         <v>80</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>81</v>
@@ -26626,10 +26629,10 @@
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -26655,20 +26658,20 @@
         <v>228</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="N191" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="O191" s="2"/>
       <c r="P191" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q191" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="R191" t="s" s="2">
         <v>80</v>
@@ -26713,7 +26716,7 @@
         <v>80</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>81</v>
@@ -26722,7 +26725,7 @@
         <v>92</v>
       </c>
       <c r="AI191" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="AJ191" t="s" s="2">
         <v>104</v>
@@ -26731,7 +26734,7 @@
         <v>80</v>
       </c>
       <c r="AL191" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="AM191" t="s" s="2">
         <v>80</v>
@@ -26740,7 +26743,7 @@
         <v>80</v>
       </c>
       <c r="AO191" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="AP191" t="s" s="2">
         <v>80</v>
@@ -26751,10 +26754,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -26780,10 +26783,10 @@
         <v>106</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="N192" s="2"/>
       <c r="O192" s="2"/>
@@ -26872,10 +26875,10 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -26991,13 +26994,13 @@
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="B194" t="s" s="2">
         <v>711</v>
       </c>
-      <c r="B194" t="s" s="2">
-        <v>710</v>
-      </c>
       <c r="C194" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="D194" t="s" s="2">
         <v>80</v>
@@ -27019,7 +27022,7 @@
         <v>80</v>
       </c>
       <c r="K194" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="L194" t="s" s="2">
         <v>385</v>
@@ -27114,10 +27117,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -27235,10 +27238,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -27358,10 +27361,10 @@
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -27401,7 +27404,7 @@
       </c>
       <c r="Q197" s="2"/>
       <c r="R197" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="S197" t="s" s="2">
         <v>80</v>
@@ -27481,10 +27484,10 @@
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -27582,7 +27585,7 @@
         <v>80</v>
       </c>
       <c r="AL198" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="AM198" t="s" s="2">
         <v>80</v>
@@ -27602,10 +27605,10 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -27723,10 +27726,10 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -27846,10 +27849,10 @@
     </row>
     <row r="201">
       <c r="A201" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -27912,10 +27915,10 @@
         <v>254</v>
       </c>
       <c r="Y201" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="Z201" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="AA201" t="s" s="2">
         <v>80</v>
@@ -27971,10 +27974,10 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -28092,10 +28095,10 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -28215,10 +28218,10 @@
     </row>
     <row r="204">
       <c r="A204" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -28340,10 +28343,10 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -28463,10 +28466,10 @@
     </row>
     <row r="206">
       <c r="A206" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -28588,10 +28591,10 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -28713,10 +28716,10 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -28838,10 +28841,10 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -28963,10 +28966,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -28992,10 +28995,10 @@
         <v>228</v>
       </c>
       <c r="L210" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="M210" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="N210" s="2"/>
       <c r="O210" s="2"/>
@@ -29046,7 +29049,7 @@
         <v>80</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="AG210" t="s" s="2">
         <v>81</v>
@@ -29084,13 +29087,13 @@
     </row>
     <row r="211">
       <c r="A211" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C211" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="D211" t="s" s="2">
         <v>80</v>
@@ -29112,16 +29115,16 @@
         <v>93</v>
       </c>
       <c r="K211" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="L211" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="M211" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="N211" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="O211" s="2"/>
       <c r="P211" t="s" s="2">
@@ -29171,7 +29174,7 @@
         <v>80</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>81</v>
@@ -29192,16 +29195,16 @@
         <v>80</v>
       </c>
       <c r="AM211" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AN211" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO211" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AP211" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AQ211" t="s" s="2">
         <v>80</v>
@@ -29209,10 +29212,10 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -29330,10 +29333,10 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -29453,13 +29456,13 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C214" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="D214" t="s" s="2">
         <v>80</v>
@@ -29481,16 +29484,16 @@
         <v>80</v>
       </c>
       <c r="K214" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="L214" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="M214" t="s" s="2">
         <v>386</v>
       </c>
       <c r="N214" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="O214" s="2"/>
       <c r="P214" t="s" s="2">
@@ -29578,10 +29581,10 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -29699,10 +29702,10 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -29822,10 +29825,10 @@
     </row>
     <row r="217">
       <c r="A217" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -29865,7 +29868,7 @@
       </c>
       <c r="Q217" s="2"/>
       <c r="R217" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="S217" t="s" s="2">
         <v>80</v>
@@ -29945,10 +29948,10 @@
     </row>
     <row r="218">
       <c r="A218" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -30066,10 +30069,10 @@
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -30187,10 +30190,10 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -30310,10 +30313,10 @@
     </row>
     <row r="221">
       <c r="A221" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -30376,10 +30379,10 @@
         <v>254</v>
       </c>
       <c r="Y221" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="Z221" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="AA221" t="s" s="2">
         <v>80</v>
@@ -30435,10 +30438,10 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -30556,10 +30559,10 @@
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -30679,10 +30682,10 @@
     </row>
     <row r="224">
       <c r="A224" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -30804,10 +30807,10 @@
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -30927,10 +30930,10 @@
     </row>
     <row r="226">
       <c r="A226" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
@@ -31052,10 +31055,10 @@
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -31177,10 +31180,10 @@
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
@@ -31302,10 +31305,10 @@
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
@@ -31427,10 +31430,10 @@
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -31453,19 +31456,19 @@
         <v>93</v>
       </c>
       <c r="K230" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="L230" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="M230" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="N230" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="O230" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="P230" t="s" s="2">
         <v>80</v>
@@ -31514,7 +31517,7 @@
         <v>80</v>
       </c>
       <c r="AF230" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="AG230" t="s" s="2">
         <v>81</v>
@@ -31541,7 +31544,7 @@
         <v>80</v>
       </c>
       <c r="AO230" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="AP230" t="s" s="2">
         <v>80</v>
@@ -31552,10 +31555,10 @@
     </row>
     <row r="231" hidden="true">
       <c r="A231" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
@@ -31581,20 +31584,20 @@
         <v>167</v>
       </c>
       <c r="L231" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="M231" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="N231" s="2"/>
       <c r="O231" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="P231" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q231" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="R231" t="s" s="2">
         <v>80</v>
@@ -31618,10 +31621,10 @@
         <v>254</v>
       </c>
       <c r="Y231" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="Z231" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="AA231" t="s" s="2">
         <v>80</v>
@@ -31639,7 +31642,7 @@
         <v>80</v>
       </c>
       <c r="AF231" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="AG231" t="s" s="2">
         <v>81</v>
@@ -31666,7 +31669,7 @@
         <v>80</v>
       </c>
       <c r="AO231" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="AP231" t="s" s="2">
         <v>80</v>
@@ -31677,10 +31680,10 @@
     </row>
     <row r="232" hidden="true">
       <c r="A232" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" t="s" s="2">
@@ -31706,14 +31709,14 @@
         <v>106</v>
       </c>
       <c r="L232" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="M232" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="N232" s="2"/>
       <c r="O232" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="P232" t="s" s="2">
         <v>80</v>
@@ -31762,7 +31765,7 @@
         <v>80</v>
       </c>
       <c r="AF232" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="AG232" t="s" s="2">
         <v>81</v>
@@ -31789,7 +31792,7 @@
         <v>80</v>
       </c>
       <c r="AO232" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="AP232" t="s" s="2">
         <v>80</v>
@@ -31800,10 +31803,10 @@
     </row>
     <row r="233" hidden="true">
       <c r="A233" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
@@ -31829,14 +31832,14 @@
         <v>133</v>
       </c>
       <c r="L233" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="M233" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="N233" s="2"/>
       <c r="O233" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="P233" t="s" s="2">
         <v>80</v>
@@ -31885,7 +31888,7 @@
         <v>80</v>
       </c>
       <c r="AF233" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="AG233" t="s" s="2">
         <v>81</v>
@@ -31894,7 +31897,7 @@
         <v>92</v>
       </c>
       <c r="AI233" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="AJ233" t="s" s="2">
         <v>104</v>
@@ -31912,7 +31915,7 @@
         <v>80</v>
       </c>
       <c r="AO233" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="AP233" t="s" s="2">
         <v>80</v>
@@ -31923,10 +31926,10 @@
     </row>
     <row r="234" hidden="true">
       <c r="A234" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
@@ -31952,16 +31955,16 @@
         <v>167</v>
       </c>
       <c r="L234" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="M234" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="N234" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="O234" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="P234" t="s" s="2">
         <v>80</v>
@@ -32010,7 +32013,7 @@
         <v>80</v>
       </c>
       <c r="AF234" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="AG234" t="s" s="2">
         <v>81</v>
@@ -32037,7 +32040,7 @@
         <v>80</v>
       </c>
       <c r="AO234" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="AP234" t="s" s="2">
         <v>80</v>
@@ -32048,10 +32051,10 @@
     </row>
     <row r="235">
       <c r="A235" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" t="s" s="2">
@@ -32074,16 +32077,16 @@
         <v>80</v>
       </c>
       <c r="K235" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="L235" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="M235" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="N235" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="O235" s="2"/>
       <c r="P235" t="s" s="2">
@@ -32133,7 +32136,7 @@
         <v>80</v>
       </c>
       <c r="AF235" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="AG235" t="s" s="2">
         <v>81</v>
@@ -32142,7 +32145,7 @@
         <v>92</v>
       </c>
       <c r="AI235" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="AJ235" t="s" s="2">
         <v>104</v>
@@ -32163,7 +32166,7 @@
         <v>80</v>
       </c>
       <c r="AP235" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="AQ235" t="s" s="2">
         <v>80</v>
@@ -32171,10 +32174,10 @@
     </row>
     <row r="236">
       <c r="A236" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
@@ -32200,10 +32203,10 @@
         <v>228</v>
       </c>
       <c r="L236" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="M236" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="N236" s="2"/>
       <c r="O236" s="2"/>
@@ -32254,7 +32257,7 @@
         <v>80</v>
       </c>
       <c r="AF236" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="AG236" t="s" s="2">
         <v>81</v>
@@ -32272,7 +32275,7 @@
         <v>80</v>
       </c>
       <c r="AL236" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="AM236" t="s" s="2">
         <v>80</v>
@@ -32281,10 +32284,10 @@
         <v>80</v>
       </c>
       <c r="AO236" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="AP236" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="AQ236" t="s" s="2">
         <v>80</v>
@@ -32292,10 +32295,10 @@
     </row>
     <row r="237">
       <c r="A237" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="C237" s="2"/>
       <c r="D237" t="s" s="2">
@@ -32318,13 +32321,13 @@
         <v>93</v>
       </c>
       <c r="K237" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="L237" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="M237" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="N237" s="2"/>
       <c r="O237" s="2"/>
@@ -32375,7 +32378,7 @@
         <v>80</v>
       </c>
       <c r="AF237" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="AG237" t="s" s="2">
         <v>81</v>
@@ -32405,7 +32408,7 @@
         <v>80</v>
       </c>
       <c r="AP237" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="AQ237" t="s" s="2">
         <v>80</v>
@@ -32413,10 +32416,10 @@
     </row>
     <row r="238">
       <c r="A238" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="C238" s="2"/>
       <c r="D238" t="s" s="2">
@@ -32439,13 +32442,13 @@
         <v>93</v>
       </c>
       <c r="K238" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="L238" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="M238" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="N238" s="2"/>
       <c r="O238" s="2"/>
@@ -32496,7 +32499,7 @@
         <v>80</v>
       </c>
       <c r="AF238" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="AG238" t="s" s="2">
         <v>81</v>
@@ -32523,10 +32526,10 @@
         <v>80</v>
       </c>
       <c r="AO238" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="AP238" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="AQ238" t="s" s="2">
         <v>80</v>
@@ -32534,10 +32537,10 @@
     </row>
     <row r="239">
       <c r="A239" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" t="s" s="2">
@@ -32560,13 +32563,13 @@
         <v>80</v>
       </c>
       <c r="K239" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="L239" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="M239" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="N239" s="2"/>
       <c r="O239" s="2"/>
@@ -32617,7 +32620,7 @@
         <v>80</v>
       </c>
       <c r="AF239" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="AG239" t="s" s="2">
         <v>81</v>
@@ -32629,7 +32632,7 @@
         <v>80</v>
       </c>
       <c r="AJ239" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="AK239" t="s" s="2">
         <v>80</v>
@@ -32655,10 +32658,10 @@
     </row>
     <row r="240" hidden="true">
       <c r="A240" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="C240" s="2"/>
       <c r="D240" t="s" s="2">
@@ -32776,10 +32779,10 @@
     </row>
     <row r="241" hidden="true">
       <c r="A241" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" t="s" s="2">
@@ -32899,14 +32902,14 @@
     </row>
     <row r="242" hidden="true">
       <c r="A242" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="C242" s="2"/>
       <c r="D242" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="E242" s="2"/>
       <c r="F242" t="s" s="2">
@@ -32928,10 +32931,10 @@
         <v>112</v>
       </c>
       <c r="L242" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="M242" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="N242" t="s" s="2">
         <v>115</v>
@@ -32986,7 +32989,7 @@
         <v>80</v>
       </c>
       <c r="AF242" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="AG242" t="s" s="2">
         <v>81</v>
@@ -33024,10 +33027,10 @@
     </row>
     <row r="243" hidden="true">
       <c r="A243" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" t="s" s="2">
@@ -33053,10 +33056,10 @@
         <v>250</v>
       </c>
       <c r="L243" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="M243" t="s" s="2">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="N243" s="2"/>
       <c r="O243" s="2"/>
@@ -33086,10 +33089,10 @@
         <v>157</v>
       </c>
       <c r="Y243" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="Z243" t="s" s="2">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="AA243" t="s" s="2">
         <v>80</v>
@@ -33107,7 +33110,7 @@
         <v>80</v>
       </c>
       <c r="AF243" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="AG243" t="s" s="2">
         <v>81</v>
@@ -33116,7 +33119,7 @@
         <v>92</v>
       </c>
       <c r="AI243" t="s" s="2">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="AJ243" t="s" s="2">
         <v>104</v>
@@ -33131,7 +33134,7 @@
         <v>80</v>
       </c>
       <c r="AN243" t="s" s="2">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="AO243" t="s" s="2">
         <v>261</v>
@@ -33145,10 +33148,10 @@
     </row>
     <row r="244" hidden="true">
       <c r="A244" t="s" s="2">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="C244" s="2"/>
       <c r="D244" t="s" s="2">
@@ -33171,13 +33174,13 @@
         <v>80</v>
       </c>
       <c r="K244" t="s" s="2">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="L244" t="s" s="2">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="M244" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="N244" s="2"/>
       <c r="O244" s="2"/>
@@ -33228,7 +33231,7 @@
         <v>80</v>
       </c>
       <c r="AF244" t="s" s="2">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="AG244" t="s" s="2">
         <v>81</v>
@@ -33237,7 +33240,7 @@
         <v>82</v>
       </c>
       <c r="AI244" t="s" s="2">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="AJ244" t="s" s="2">
         <v>104</v>
@@ -33266,10 +33269,10 @@
     </row>
     <row r="245" hidden="true">
       <c r="A245" t="s" s="2">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="C245" s="2"/>
       <c r="D245" t="s" s="2">
@@ -33295,10 +33298,10 @@
         <v>250</v>
       </c>
       <c r="L245" t="s" s="2">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="M245" t="s" s="2">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="N245" s="2"/>
       <c r="O245" s="2"/>
@@ -33328,10 +33331,10 @@
         <v>157</v>
       </c>
       <c r="Y245" t="s" s="2">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="Z245" t="s" s="2">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="AA245" t="s" s="2">
         <v>80</v>
@@ -33349,7 +33352,7 @@
         <v>80</v>
       </c>
       <c r="AF245" t="s" s="2">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="AG245" t="s" s="2">
         <v>81</v>
@@ -33387,10 +33390,10 @@
     </row>
     <row r="246">
       <c r="A246" t="s" s="2">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="C246" s="2"/>
       <c r="D246" t="s" s="2">
@@ -33413,16 +33416,16 @@
         <v>80</v>
       </c>
       <c r="K246" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="L246" t="s" s="2">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="M246" t="s" s="2">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="N246" t="s" s="2">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="O246" s="2"/>
       <c r="P246" t="s" s="2">
@@ -33472,7 +33475,7 @@
         <v>80</v>
       </c>
       <c r="AF246" t="s" s="2">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="AG246" t="s" s="2">
         <v>81</v>
@@ -33484,7 +33487,7 @@
         <v>80</v>
       </c>
       <c r="AJ246" t="s" s="2">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="AK246" t="s" s="2">
         <v>80</v>
@@ -33510,10 +33513,10 @@
     </row>
     <row r="247" hidden="true">
       <c r="A247" t="s" s="2">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="C247" s="2"/>
       <c r="D247" t="s" s="2">
@@ -33631,10 +33634,10 @@
     </row>
     <row r="248" hidden="true">
       <c r="A248" t="s" s="2">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B248" t="s" s="2">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="C248" s="2"/>
       <c r="D248" t="s" s="2">
@@ -33754,14 +33757,14 @@
     </row>
     <row r="249" hidden="true">
       <c r="A249" t="s" s="2">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="B249" t="s" s="2">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="C249" s="2"/>
       <c r="D249" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="E249" s="2"/>
       <c r="F249" t="s" s="2">
@@ -33783,10 +33786,10 @@
         <v>112</v>
       </c>
       <c r="L249" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="M249" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="N249" t="s" s="2">
         <v>115</v>
@@ -33841,7 +33844,7 @@
         <v>80</v>
       </c>
       <c r="AF249" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="AG249" t="s" s="2">
         <v>81</v>
@@ -33879,10 +33882,10 @@
     </row>
     <row r="250">
       <c r="A250" t="s" s="2">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="B250" t="s" s="2">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="C250" s="2"/>
       <c r="D250" t="s" s="2">
@@ -33908,10 +33911,10 @@
         <v>250</v>
       </c>
       <c r="L250" t="s" s="2">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="M250" t="s" s="2">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="N250" s="2"/>
       <c r="O250" s="2"/>
@@ -33941,10 +33944,10 @@
         <v>157</v>
       </c>
       <c r="Y250" t="s" s="2">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="Z250" t="s" s="2">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="AA250" t="s" s="2">
         <v>80</v>
@@ -33962,7 +33965,7 @@
         <v>80</v>
       </c>
       <c r="AF250" t="s" s="2">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="AG250" t="s" s="2">
         <v>81</v>
@@ -33971,19 +33974,19 @@
         <v>82</v>
       </c>
       <c r="AI250" t="s" s="2">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="AJ250" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK250" t="s" s="2">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="AL250" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM250" t="s" s="2">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="AN250" t="s" s="2">
         <v>342</v>
@@ -33992,7 +33995,7 @@
         <v>80</v>
       </c>
       <c r="AP250" t="s" s="2">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="AQ250" t="s" s="2">
         <v>80</v>
@@ -34000,10 +34003,10 @@
     </row>
     <row r="251" hidden="true">
       <c r="A251" t="s" s="2">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="B251" t="s" s="2">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="C251" s="2"/>
       <c r="D251" t="s" s="2">
@@ -34121,10 +34124,10 @@
     </row>
     <row r="252" hidden="true">
       <c r="A252" t="s" s="2">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="B252" t="s" s="2">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="C252" s="2"/>
       <c r="D252" t="s" s="2">
@@ -34244,10 +34247,10 @@
     </row>
     <row r="253" hidden="true">
       <c r="A253" t="s" s="2">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="B253" t="s" s="2">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="C253" s="2"/>
       <c r="D253" t="s" s="2">
@@ -34367,13 +34370,13 @@
     </row>
     <row r="254">
       <c r="A254" t="s" s="2">
+        <v>899</v>
+      </c>
+      <c r="B254" t="s" s="2">
         <v>898</v>
       </c>
-      <c r="B254" t="s" s="2">
-        <v>897</v>
-      </c>
       <c r="C254" t="s" s="2">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="D254" t="s" s="2">
         <v>80</v>
@@ -34398,7 +34401,7 @@
         <v>145</v>
       </c>
       <c r="L254" t="s" s="2">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="M254" t="s" s="2">
         <v>267</v>
@@ -34417,7 +34420,7 @@
         <v>80</v>
       </c>
       <c r="S254" t="s" s="2">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="T254" t="s" s="2">
         <v>80</v>
@@ -34494,10 +34497,10 @@
     </row>
     <row r="255" hidden="true">
       <c r="A255" t="s" s="2">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="B255" t="s" s="2">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="C255" s="2"/>
       <c r="D255" t="s" s="2">
@@ -34619,10 +34622,10 @@
     </row>
     <row r="256">
       <c r="A256" t="s" s="2">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="B256" t="s" s="2">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="C256" s="2"/>
       <c r="D256" t="s" s="2">
@@ -34645,16 +34648,16 @@
         <v>93</v>
       </c>
       <c r="K256" t="s" s="2">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="L256" t="s" s="2">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="M256" t="s" s="2">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="N256" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="O256" s="2"/>
       <c r="P256" t="s" s="2">
@@ -34704,7 +34707,7 @@
         <v>80</v>
       </c>
       <c r="AF256" t="s" s="2">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="AG256" t="s" s="2">
         <v>81</v>
@@ -34713,13 +34716,13 @@
         <v>82</v>
       </c>
       <c r="AI256" t="s" s="2">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="AJ256" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK256" t="s" s="2">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="AL256" t="s" s="2">
         <v>80</v>
@@ -34734,7 +34737,7 @@
         <v>80</v>
       </c>
       <c r="AP256" t="s" s="2">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="AQ256" t="s" s="2">
         <v>80</v>
@@ -34742,10 +34745,10 @@
     </row>
     <row r="257">
       <c r="A257" t="s" s="2">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="B257" t="s" s="2">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="C257" s="2"/>
       <c r="D257" t="s" s="2">
@@ -34768,13 +34771,13 @@
         <v>80</v>
       </c>
       <c r="K257" t="s" s="2">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="L257" t="s" s="2">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="M257" t="s" s="2">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="N257" s="2"/>
       <c r="O257" s="2"/>
@@ -34825,7 +34828,7 @@
         <v>80</v>
       </c>
       <c r="AF257" t="s" s="2">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="AG257" t="s" s="2">
         <v>81</v>
@@ -34843,16 +34846,16 @@
         <v>80</v>
       </c>
       <c r="AL257" t="s" s="2">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="AM257" t="s" s="2">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="AN257" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AO257" t="s" s="2">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="AP257" t="s" s="2">
         <v>80</v>

--- a/branches/dev/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
+++ b/branches/dev/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T10:52:45+00:00</t>
+    <t>2026-09-11T12:45:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
+++ b/branches/dev/StructureDefinition-mii-pr-seltene-genetic-diagnosis.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10070" uniqueCount="917">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10071" uniqueCount="917">
   <si>
     <t>Property</t>
   </si>
@@ -57,10 +57,13 @@
     <t>Experimental</t>
   </si>
   <si>
+    <t>false</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T12:45:52+00:00</t>
+    <t>2026-09-11T14:10:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -118,9 +121,6 @@
   </si>
   <si>
     <t>Abstract</t>
-  </si>
-  <si>
-    <t>false</t>
   </si>
   <si>
     <t>Derivation</t>
@@ -3077,98 +3077,100 @@
       <c r="A7" t="s" s="2">
         <v>12</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>34</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20">
@@ -3366,10 +3368,10 @@
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
@@ -3449,7 +3451,7 @@
         <v>80</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AG2" t="s" s="2">
         <v>81</v>
